--- a/artkal-m-221-official/colors.xlsx
+++ b/artkal-m-221-official/colors.xlsx
@@ -2489,12 +2489,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>原始查询名</t>
+          <t>系列短名</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>优肯418色中的 M221</t>
+          <t>优肯M221色</t>
         </is>
       </c>
     </row>

--- a/artkal-m-221-official/colors.xlsx
+++ b/artkal-m-221-official/colors.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_MA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_MB" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_MC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_ME" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MG" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_MH" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_MM" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_MA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_MB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_MC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_MD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_ME" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_MF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_MG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_MH" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_MM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/artkal-m-221-official/colors.xlsx
+++ b/artkal-m-221-official/colors.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_MA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_MB" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_MC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_MD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_ME" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_MF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_MG" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_MH" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_MM" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_MA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_MB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_MC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_ME" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_MH" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_MM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,7 +59,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="223">
+  <fills count="222">
     <fill>
       <patternFill/>
     </fill>
@@ -979,11 +979,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBF8C6E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1198,7 +1193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="450">
+  <cellXfs count="448">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1951,7 +1946,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="186" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="187" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="187" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="187" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1967,7 +1962,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="190" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="191" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1999,11 +1994,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="198" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="199" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="199" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="199" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="200" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="200" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="200" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2035,7 +2030,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="207" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="208" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="208" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="208" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2043,7 +2038,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="209" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="210" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="210" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="210" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2059,11 +2054,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="213" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="214" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="214" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="214" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="215" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="215" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="215" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2075,26 +2070,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="217" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="218" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="218" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="218" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="219" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="219" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="219" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="220" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="220" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="220" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="221" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="221" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="221" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="222" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="222" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2460,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2527,17 +2518,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>无 RGB / 透明或未公开</t>
+          <t>无 RGB / 未填数值</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2582,6 +2573,13 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/1323/8195/files/M_MINI_Beads_RGB_Color_Chart_2025.pdf?v=1760661747</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://bitbead.pomodiary.com/zh/colors/artkal-mini/MH1</t>
         </is>
       </c>
     </row>
@@ -2635,56 +2633,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="420" t="inlineStr">
+      <c r="A4" s="418" t="inlineStr">
         <is>
           <t>MM1</t>
         </is>
       </c>
-      <c r="B4" s="421" t="n"/>
-      <c r="C4" s="421" t="n"/>
-      <c r="D4" s="421" t="n"/>
-      <c r="F4" s="422" t="inlineStr">
+      <c r="B4" s="419" t="n"/>
+      <c r="C4" s="419" t="n"/>
+      <c r="D4" s="419" t="n"/>
+      <c r="F4" s="420" t="inlineStr">
         <is>
           <t>MM2</t>
         </is>
       </c>
-      <c r="G4" s="423" t="n"/>
-      <c r="H4" s="423" t="n"/>
-      <c r="I4" s="423" t="n"/>
-      <c r="K4" s="424" t="inlineStr">
+      <c r="G4" s="421" t="n"/>
+      <c r="H4" s="421" t="n"/>
+      <c r="I4" s="421" t="n"/>
+      <c r="K4" s="422" t="inlineStr">
         <is>
           <t>MM3</t>
         </is>
       </c>
-      <c r="L4" s="425" t="n"/>
-      <c r="M4" s="425" t="n"/>
-      <c r="N4" s="425" t="n"/>
-      <c r="P4" s="426" t="inlineStr">
+      <c r="L4" s="423" t="n"/>
+      <c r="M4" s="423" t="n"/>
+      <c r="N4" s="423" t="n"/>
+      <c r="P4" s="424" t="inlineStr">
         <is>
           <t>MM4</t>
         </is>
       </c>
-      <c r="Q4" s="427" t="n"/>
-      <c r="R4" s="427" t="n"/>
-      <c r="S4" s="427" t="n"/>
+      <c r="Q4" s="425" t="n"/>
+      <c r="R4" s="425" t="n"/>
+      <c r="S4" s="425" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="421" t="n"/>
-      <c r="B5" s="421" t="n"/>
-      <c r="C5" s="421" t="n"/>
-      <c r="D5" s="421" t="n"/>
-      <c r="F5" s="423" t="n"/>
-      <c r="G5" s="423" t="n"/>
-      <c r="H5" s="423" t="n"/>
-      <c r="I5" s="423" t="n"/>
-      <c r="K5" s="425" t="n"/>
-      <c r="L5" s="425" t="n"/>
-      <c r="M5" s="425" t="n"/>
-      <c r="N5" s="425" t="n"/>
-      <c r="P5" s="427" t="n"/>
-      <c r="Q5" s="427" t="n"/>
-      <c r="R5" s="427" t="n"/>
-      <c r="S5" s="427" t="n"/>
+      <c r="A5" s="419" t="n"/>
+      <c r="B5" s="419" t="n"/>
+      <c r="C5" s="419" t="n"/>
+      <c r="D5" s="419" t="n"/>
+      <c r="F5" s="421" t="n"/>
+      <c r="G5" s="421" t="n"/>
+      <c r="H5" s="421" t="n"/>
+      <c r="I5" s="421" t="n"/>
+      <c r="K5" s="423" t="n"/>
+      <c r="L5" s="423" t="n"/>
+      <c r="M5" s="423" t="n"/>
+      <c r="N5" s="423" t="n"/>
+      <c r="P5" s="425" t="n"/>
+      <c r="Q5" s="425" t="n"/>
+      <c r="R5" s="425" t="n"/>
+      <c r="S5" s="425" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -2789,56 +2787,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="428" t="inlineStr">
+      <c r="A9" s="426" t="inlineStr">
         <is>
           <t>MM5</t>
         </is>
       </c>
-      <c r="B9" s="429" t="n"/>
-      <c r="C9" s="429" t="n"/>
-      <c r="D9" s="429" t="n"/>
-      <c r="F9" s="430" t="inlineStr">
+      <c r="B9" s="427" t="n"/>
+      <c r="C9" s="427" t="n"/>
+      <c r="D9" s="427" t="n"/>
+      <c r="F9" s="428" t="inlineStr">
         <is>
           <t>MM6</t>
         </is>
       </c>
-      <c r="G9" s="431" t="n"/>
-      <c r="H9" s="431" t="n"/>
-      <c r="I9" s="431" t="n"/>
-      <c r="K9" s="432" t="inlineStr">
+      <c r="G9" s="429" t="n"/>
+      <c r="H9" s="429" t="n"/>
+      <c r="I9" s="429" t="n"/>
+      <c r="K9" s="430" t="inlineStr">
         <is>
           <t>MM7</t>
         </is>
       </c>
-      <c r="L9" s="433" t="n"/>
-      <c r="M9" s="433" t="n"/>
-      <c r="N9" s="433" t="n"/>
-      <c r="P9" s="434" t="inlineStr">
+      <c r="L9" s="431" t="n"/>
+      <c r="M9" s="431" t="n"/>
+      <c r="N9" s="431" t="n"/>
+      <c r="P9" s="432" t="inlineStr">
         <is>
           <t>MM8</t>
         </is>
       </c>
-      <c r="Q9" s="435" t="n"/>
-      <c r="R9" s="435" t="n"/>
-      <c r="S9" s="435" t="n"/>
+      <c r="Q9" s="433" t="n"/>
+      <c r="R9" s="433" t="n"/>
+      <c r="S9" s="433" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="429" t="n"/>
-      <c r="B10" s="429" t="n"/>
-      <c r="C10" s="429" t="n"/>
-      <c r="D10" s="429" t="n"/>
-      <c r="F10" s="431" t="n"/>
-      <c r="G10" s="431" t="n"/>
-      <c r="H10" s="431" t="n"/>
-      <c r="I10" s="431" t="n"/>
-      <c r="K10" s="433" t="n"/>
-      <c r="L10" s="433" t="n"/>
-      <c r="M10" s="433" t="n"/>
-      <c r="N10" s="433" t="n"/>
-      <c r="P10" s="435" t="n"/>
-      <c r="Q10" s="435" t="n"/>
-      <c r="R10" s="435" t="n"/>
-      <c r="S10" s="435" t="n"/>
+      <c r="A10" s="427" t="n"/>
+      <c r="B10" s="427" t="n"/>
+      <c r="C10" s="427" t="n"/>
+      <c r="D10" s="427" t="n"/>
+      <c r="F10" s="429" t="n"/>
+      <c r="G10" s="429" t="n"/>
+      <c r="H10" s="429" t="n"/>
+      <c r="I10" s="429" t="n"/>
+      <c r="K10" s="431" t="n"/>
+      <c r="L10" s="431" t="n"/>
+      <c r="M10" s="431" t="n"/>
+      <c r="N10" s="431" t="n"/>
+      <c r="P10" s="433" t="n"/>
+      <c r="Q10" s="433" t="n"/>
+      <c r="R10" s="433" t="n"/>
+      <c r="S10" s="433" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -2943,56 +2941,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="436" t="inlineStr">
+      <c r="A14" s="434" t="inlineStr">
         <is>
           <t>MM9</t>
         </is>
       </c>
-      <c r="B14" s="437" t="n"/>
-      <c r="C14" s="437" t="n"/>
-      <c r="D14" s="437" t="n"/>
-      <c r="F14" s="438" t="inlineStr">
+      <c r="B14" s="435" t="n"/>
+      <c r="C14" s="435" t="n"/>
+      <c r="D14" s="435" t="n"/>
+      <c r="F14" s="436" t="inlineStr">
         <is>
           <t>MM10</t>
         </is>
       </c>
-      <c r="G14" s="439" t="n"/>
-      <c r="H14" s="439" t="n"/>
-      <c r="I14" s="439" t="n"/>
-      <c r="K14" s="440" t="inlineStr">
+      <c r="G14" s="437" t="n"/>
+      <c r="H14" s="437" t="n"/>
+      <c r="I14" s="437" t="n"/>
+      <c r="K14" s="438" t="inlineStr">
         <is>
           <t>MM11</t>
         </is>
       </c>
-      <c r="L14" s="441" t="n"/>
-      <c r="M14" s="441" t="n"/>
-      <c r="N14" s="441" t="n"/>
-      <c r="P14" s="442" t="inlineStr">
+      <c r="L14" s="439" t="n"/>
+      <c r="M14" s="439" t="n"/>
+      <c r="N14" s="439" t="n"/>
+      <c r="P14" s="440" t="inlineStr">
         <is>
           <t>MM12</t>
         </is>
       </c>
-      <c r="Q14" s="443" t="n"/>
-      <c r="R14" s="443" t="n"/>
-      <c r="S14" s="443" t="n"/>
+      <c r="Q14" s="441" t="n"/>
+      <c r="R14" s="441" t="n"/>
+      <c r="S14" s="441" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="437" t="n"/>
-      <c r="B15" s="437" t="n"/>
-      <c r="C15" s="437" t="n"/>
-      <c r="D15" s="437" t="n"/>
-      <c r="F15" s="439" t="n"/>
-      <c r="G15" s="439" t="n"/>
-      <c r="H15" s="439" t="n"/>
-      <c r="I15" s="439" t="n"/>
-      <c r="K15" s="441" t="n"/>
-      <c r="L15" s="441" t="n"/>
-      <c r="M15" s="441" t="n"/>
-      <c r="N15" s="441" t="n"/>
-      <c r="P15" s="443" t="n"/>
-      <c r="Q15" s="443" t="n"/>
-      <c r="R15" s="443" t="n"/>
-      <c r="S15" s="443" t="n"/>
+      <c r="A15" s="435" t="n"/>
+      <c r="B15" s="435" t="n"/>
+      <c r="C15" s="435" t="n"/>
+      <c r="D15" s="435" t="n"/>
+      <c r="F15" s="437" t="n"/>
+      <c r="G15" s="437" t="n"/>
+      <c r="H15" s="437" t="n"/>
+      <c r="I15" s="437" t="n"/>
+      <c r="K15" s="439" t="n"/>
+      <c r="L15" s="439" t="n"/>
+      <c r="M15" s="439" t="n"/>
+      <c r="N15" s="439" t="n"/>
+      <c r="P15" s="441" t="n"/>
+      <c r="Q15" s="441" t="n"/>
+      <c r="R15" s="441" t="n"/>
+      <c r="S15" s="441" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3097,44 +3095,44 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="444" t="inlineStr">
+      <c r="A19" s="442" t="inlineStr">
         <is>
           <t>MM13</t>
         </is>
       </c>
-      <c r="B19" s="445" t="n"/>
-      <c r="C19" s="445" t="n"/>
-      <c r="D19" s="445" t="n"/>
-      <c r="F19" s="446" t="inlineStr">
+      <c r="B19" s="443" t="n"/>
+      <c r="C19" s="443" t="n"/>
+      <c r="D19" s="443" t="n"/>
+      <c r="F19" s="444" t="inlineStr">
         <is>
           <t>MM14</t>
         </is>
       </c>
-      <c r="G19" s="447" t="n"/>
-      <c r="H19" s="447" t="n"/>
-      <c r="I19" s="447" t="n"/>
-      <c r="K19" s="448" t="inlineStr">
+      <c r="G19" s="445" t="n"/>
+      <c r="H19" s="445" t="n"/>
+      <c r="I19" s="445" t="n"/>
+      <c r="K19" s="446" t="inlineStr">
         <is>
           <t>MM15</t>
         </is>
       </c>
-      <c r="L19" s="449" t="n"/>
-      <c r="M19" s="449" t="n"/>
-      <c r="N19" s="449" t="n"/>
+      <c r="L19" s="447" t="n"/>
+      <c r="M19" s="447" t="n"/>
+      <c r="N19" s="447" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="445" t="n"/>
-      <c r="B20" s="445" t="n"/>
-      <c r="C20" s="445" t="n"/>
-      <c r="D20" s="445" t="n"/>
-      <c r="F20" s="447" t="n"/>
-      <c r="G20" s="447" t="n"/>
-      <c r="H20" s="447" t="n"/>
-      <c r="I20" s="447" t="n"/>
-      <c r="K20" s="449" t="n"/>
-      <c r="L20" s="449" t="n"/>
-      <c r="M20" s="449" t="n"/>
-      <c r="N20" s="449" t="n"/>
+      <c r="A20" s="443" t="n"/>
+      <c r="B20" s="443" t="n"/>
+      <c r="C20" s="443" t="n"/>
+      <c r="D20" s="443" t="n"/>
+      <c r="F20" s="445" t="n"/>
+      <c r="G20" s="445" t="n"/>
+      <c r="H20" s="445" t="n"/>
+      <c r="I20" s="445" t="n"/>
+      <c r="K20" s="447" t="n"/>
+      <c r="L20" s="447" t="n"/>
+      <c r="M20" s="447" t="n"/>
+      <c r="N20" s="447" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -11501,53 +11499,53 @@
       <c r="B4" s="375" t="n"/>
       <c r="C4" s="375" t="n"/>
       <c r="D4" s="375" t="n"/>
-      <c r="F4" s="376" t="inlineStr">
+      <c r="F4" s="374" t="inlineStr">
         <is>
           <t>MH2</t>
         </is>
       </c>
-      <c r="G4" s="377" t="n"/>
-      <c r="H4" s="377" t="n"/>
-      <c r="I4" s="377" t="n"/>
-      <c r="K4" s="378" t="inlineStr">
+      <c r="G4" s="375" t="n"/>
+      <c r="H4" s="375" t="n"/>
+      <c r="I4" s="375" t="n"/>
+      <c r="K4" s="376" t="inlineStr">
         <is>
           <t>MH3</t>
         </is>
       </c>
-      <c r="L4" s="379" t="n"/>
-      <c r="M4" s="379" t="n"/>
-      <c r="N4" s="379" t="n"/>
-      <c r="P4" s="380" t="inlineStr">
+      <c r="L4" s="377" t="n"/>
+      <c r="M4" s="377" t="n"/>
+      <c r="N4" s="377" t="n"/>
+      <c r="P4" s="378" t="inlineStr">
         <is>
           <t>MH4</t>
         </is>
       </c>
-      <c r="Q4" s="381" t="n"/>
-      <c r="R4" s="381" t="n"/>
-      <c r="S4" s="381" t="n"/>
+      <c r="Q4" s="379" t="n"/>
+      <c r="R4" s="379" t="n"/>
+      <c r="S4" s="379" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="375" t="n"/>
       <c r="B5" s="375" t="n"/>
       <c r="C5" s="375" t="n"/>
       <c r="D5" s="375" t="n"/>
-      <c r="F5" s="377" t="n"/>
-      <c r="G5" s="377" t="n"/>
-      <c r="H5" s="377" t="n"/>
-      <c r="I5" s="377" t="n"/>
-      <c r="K5" s="379" t="n"/>
-      <c r="L5" s="379" t="n"/>
-      <c r="M5" s="379" t="n"/>
-      <c r="N5" s="379" t="n"/>
-      <c r="P5" s="381" t="n"/>
-      <c r="Q5" s="381" t="n"/>
-      <c r="R5" s="381" t="n"/>
-      <c r="S5" s="381" t="n"/>
+      <c r="F5" s="375" t="n"/>
+      <c r="G5" s="375" t="n"/>
+      <c r="H5" s="375" t="n"/>
+      <c r="I5" s="375" t="n"/>
+      <c r="K5" s="377" t="n"/>
+      <c r="L5" s="377" t="n"/>
+      <c r="M5" s="377" t="n"/>
+      <c r="N5" s="377" t="n"/>
+      <c r="P5" s="379" t="n"/>
+      <c r="Q5" s="379" t="n"/>
+      <c r="R5" s="379" t="n"/>
+      <c r="S5" s="379" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #FFFFFF</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -11581,7 +11579,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 255, 255, 255</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -11615,7 +11613,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_pdf</t>
+          <t>来源: public_tool_display_hex</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
@@ -11647,56 +11645,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="382" t="inlineStr">
+      <c r="A9" s="380" t="inlineStr">
         <is>
           <t>MH5</t>
         </is>
       </c>
-      <c r="B9" s="383" t="n"/>
-      <c r="C9" s="383" t="n"/>
-      <c r="D9" s="383" t="n"/>
-      <c r="F9" s="384" t="inlineStr">
+      <c r="B9" s="381" t="n"/>
+      <c r="C9" s="381" t="n"/>
+      <c r="D9" s="381" t="n"/>
+      <c r="F9" s="382" t="inlineStr">
         <is>
           <t>MH6</t>
         </is>
       </c>
-      <c r="G9" s="385" t="n"/>
-      <c r="H9" s="385" t="n"/>
-      <c r="I9" s="385" t="n"/>
-      <c r="K9" s="386" t="inlineStr">
+      <c r="G9" s="383" t="n"/>
+      <c r="H9" s="383" t="n"/>
+      <c r="I9" s="383" t="n"/>
+      <c r="K9" s="384" t="inlineStr">
         <is>
           <t>MH7</t>
         </is>
       </c>
-      <c r="L9" s="387" t="n"/>
-      <c r="M9" s="387" t="n"/>
-      <c r="N9" s="387" t="n"/>
-      <c r="P9" s="388" t="inlineStr">
+      <c r="L9" s="385" t="n"/>
+      <c r="M9" s="385" t="n"/>
+      <c r="N9" s="385" t="n"/>
+      <c r="P9" s="386" t="inlineStr">
         <is>
           <t>MH8</t>
         </is>
       </c>
-      <c r="Q9" s="389" t="n"/>
-      <c r="R9" s="389" t="n"/>
-      <c r="S9" s="389" t="n"/>
+      <c r="Q9" s="387" t="n"/>
+      <c r="R9" s="387" t="n"/>
+      <c r="S9" s="387" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="383" t="n"/>
-      <c r="B10" s="383" t="n"/>
-      <c r="C10" s="383" t="n"/>
-      <c r="D10" s="383" t="n"/>
-      <c r="F10" s="385" t="n"/>
-      <c r="G10" s="385" t="n"/>
-      <c r="H10" s="385" t="n"/>
-      <c r="I10" s="385" t="n"/>
-      <c r="K10" s="387" t="n"/>
-      <c r="L10" s="387" t="n"/>
-      <c r="M10" s="387" t="n"/>
-      <c r="N10" s="387" t="n"/>
-      <c r="P10" s="389" t="n"/>
-      <c r="Q10" s="389" t="n"/>
-      <c r="R10" s="389" t="n"/>
-      <c r="S10" s="389" t="n"/>
+      <c r="A10" s="381" t="n"/>
+      <c r="B10" s="381" t="n"/>
+      <c r="C10" s="381" t="n"/>
+      <c r="D10" s="381" t="n"/>
+      <c r="F10" s="383" t="n"/>
+      <c r="G10" s="383" t="n"/>
+      <c r="H10" s="383" t="n"/>
+      <c r="I10" s="383" t="n"/>
+      <c r="K10" s="385" t="n"/>
+      <c r="L10" s="385" t="n"/>
+      <c r="M10" s="385" t="n"/>
+      <c r="N10" s="385" t="n"/>
+      <c r="P10" s="387" t="n"/>
+      <c r="Q10" s="387" t="n"/>
+      <c r="R10" s="387" t="n"/>
+      <c r="S10" s="387" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -11801,56 +11799,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="390" t="inlineStr">
+      <c r="A14" s="388" t="inlineStr">
         <is>
           <t>MH9</t>
         </is>
       </c>
-      <c r="B14" s="391" t="n"/>
-      <c r="C14" s="391" t="n"/>
-      <c r="D14" s="391" t="n"/>
-      <c r="F14" s="392" t="inlineStr">
+      <c r="B14" s="389" t="n"/>
+      <c r="C14" s="389" t="n"/>
+      <c r="D14" s="389" t="n"/>
+      <c r="F14" s="390" t="inlineStr">
         <is>
           <t>MH10</t>
         </is>
       </c>
-      <c r="G14" s="393" t="n"/>
-      <c r="H14" s="393" t="n"/>
-      <c r="I14" s="393" t="n"/>
-      <c r="K14" s="394" t="inlineStr">
+      <c r="G14" s="391" t="n"/>
+      <c r="H14" s="391" t="n"/>
+      <c r="I14" s="391" t="n"/>
+      <c r="K14" s="392" t="inlineStr">
         <is>
           <t>MH11</t>
         </is>
       </c>
-      <c r="L14" s="395" t="n"/>
-      <c r="M14" s="395" t="n"/>
-      <c r="N14" s="395" t="n"/>
-      <c r="P14" s="396" t="inlineStr">
+      <c r="L14" s="393" t="n"/>
+      <c r="M14" s="393" t="n"/>
+      <c r="N14" s="393" t="n"/>
+      <c r="P14" s="394" t="inlineStr">
         <is>
           <t>MH12</t>
         </is>
       </c>
-      <c r="Q14" s="397" t="n"/>
-      <c r="R14" s="397" t="n"/>
-      <c r="S14" s="397" t="n"/>
+      <c r="Q14" s="395" t="n"/>
+      <c r="R14" s="395" t="n"/>
+      <c r="S14" s="395" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="391" t="n"/>
-      <c r="B15" s="391" t="n"/>
-      <c r="C15" s="391" t="n"/>
-      <c r="D15" s="391" t="n"/>
-      <c r="F15" s="393" t="n"/>
-      <c r="G15" s="393" t="n"/>
-      <c r="H15" s="393" t="n"/>
-      <c r="I15" s="393" t="n"/>
-      <c r="K15" s="395" t="n"/>
-      <c r="L15" s="395" t="n"/>
-      <c r="M15" s="395" t="n"/>
-      <c r="N15" s="395" t="n"/>
-      <c r="P15" s="397" t="n"/>
-      <c r="Q15" s="397" t="n"/>
-      <c r="R15" s="397" t="n"/>
-      <c r="S15" s="397" t="n"/>
+      <c r="A15" s="389" t="n"/>
+      <c r="B15" s="389" t="n"/>
+      <c r="C15" s="389" t="n"/>
+      <c r="D15" s="389" t="n"/>
+      <c r="F15" s="391" t="n"/>
+      <c r="G15" s="391" t="n"/>
+      <c r="H15" s="391" t="n"/>
+      <c r="I15" s="391" t="n"/>
+      <c r="K15" s="393" t="n"/>
+      <c r="L15" s="393" t="n"/>
+      <c r="M15" s="393" t="n"/>
+      <c r="N15" s="393" t="n"/>
+      <c r="P15" s="395" t="n"/>
+      <c r="Q15" s="395" t="n"/>
+      <c r="R15" s="395" t="n"/>
+      <c r="S15" s="395" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -11955,56 +11953,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="398" t="inlineStr">
+      <c r="A19" s="396" t="inlineStr">
         <is>
           <t>MH13</t>
         </is>
       </c>
-      <c r="B19" s="399" t="n"/>
-      <c r="C19" s="399" t="n"/>
-      <c r="D19" s="399" t="n"/>
-      <c r="F19" s="400" t="inlineStr">
+      <c r="B19" s="397" t="n"/>
+      <c r="C19" s="397" t="n"/>
+      <c r="D19" s="397" t="n"/>
+      <c r="F19" s="398" t="inlineStr">
         <is>
           <t>MH14</t>
         </is>
       </c>
-      <c r="G19" s="401" t="n"/>
-      <c r="H19" s="401" t="n"/>
-      <c r="I19" s="401" t="n"/>
-      <c r="K19" s="402" t="inlineStr">
+      <c r="G19" s="399" t="n"/>
+      <c r="H19" s="399" t="n"/>
+      <c r="I19" s="399" t="n"/>
+      <c r="K19" s="400" t="inlineStr">
         <is>
           <t>MH15</t>
         </is>
       </c>
-      <c r="L19" s="403" t="n"/>
-      <c r="M19" s="403" t="n"/>
-      <c r="N19" s="403" t="n"/>
-      <c r="P19" s="404" t="inlineStr">
+      <c r="L19" s="401" t="n"/>
+      <c r="M19" s="401" t="n"/>
+      <c r="N19" s="401" t="n"/>
+      <c r="P19" s="402" t="inlineStr">
         <is>
           <t>MH16</t>
         </is>
       </c>
-      <c r="Q19" s="405" t="n"/>
-      <c r="R19" s="405" t="n"/>
-      <c r="S19" s="405" t="n"/>
+      <c r="Q19" s="403" t="n"/>
+      <c r="R19" s="403" t="n"/>
+      <c r="S19" s="403" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="399" t="n"/>
-      <c r="B20" s="399" t="n"/>
-      <c r="C20" s="399" t="n"/>
-      <c r="D20" s="399" t="n"/>
-      <c r="F20" s="401" t="n"/>
-      <c r="G20" s="401" t="n"/>
-      <c r="H20" s="401" t="n"/>
-      <c r="I20" s="401" t="n"/>
-      <c r="K20" s="403" t="n"/>
-      <c r="L20" s="403" t="n"/>
-      <c r="M20" s="403" t="n"/>
-      <c r="N20" s="403" t="n"/>
-      <c r="P20" s="405" t="n"/>
-      <c r="Q20" s="405" t="n"/>
-      <c r="R20" s="405" t="n"/>
-      <c r="S20" s="405" t="n"/>
+      <c r="A20" s="397" t="n"/>
+      <c r="B20" s="397" t="n"/>
+      <c r="C20" s="397" t="n"/>
+      <c r="D20" s="397" t="n"/>
+      <c r="F20" s="399" t="n"/>
+      <c r="G20" s="399" t="n"/>
+      <c r="H20" s="399" t="n"/>
+      <c r="I20" s="399" t="n"/>
+      <c r="K20" s="401" t="n"/>
+      <c r="L20" s="401" t="n"/>
+      <c r="M20" s="401" t="n"/>
+      <c r="N20" s="401" t="n"/>
+      <c r="P20" s="403" t="n"/>
+      <c r="Q20" s="403" t="n"/>
+      <c r="R20" s="403" t="n"/>
+      <c r="S20" s="403" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -12109,56 +12107,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="406" t="inlineStr">
+      <c r="A24" s="404" t="inlineStr">
         <is>
           <t>MH17</t>
         </is>
       </c>
-      <c r="B24" s="407" t="n"/>
-      <c r="C24" s="407" t="n"/>
-      <c r="D24" s="407" t="n"/>
-      <c r="F24" s="408" t="inlineStr">
+      <c r="B24" s="405" t="n"/>
+      <c r="C24" s="405" t="n"/>
+      <c r="D24" s="405" t="n"/>
+      <c r="F24" s="406" t="inlineStr">
         <is>
           <t>MH18</t>
         </is>
       </c>
-      <c r="G24" s="409" t="n"/>
-      <c r="H24" s="409" t="n"/>
-      <c r="I24" s="409" t="n"/>
-      <c r="K24" s="410" t="inlineStr">
+      <c r="G24" s="407" t="n"/>
+      <c r="H24" s="407" t="n"/>
+      <c r="I24" s="407" t="n"/>
+      <c r="K24" s="408" t="inlineStr">
         <is>
           <t>MH19</t>
         </is>
       </c>
-      <c r="L24" s="411" t="n"/>
-      <c r="M24" s="411" t="n"/>
-      <c r="N24" s="411" t="n"/>
-      <c r="P24" s="412" t="inlineStr">
+      <c r="L24" s="409" t="n"/>
+      <c r="M24" s="409" t="n"/>
+      <c r="N24" s="409" t="n"/>
+      <c r="P24" s="410" t="inlineStr">
         <is>
           <t>MH20</t>
         </is>
       </c>
-      <c r="Q24" s="413" t="n"/>
-      <c r="R24" s="413" t="n"/>
-      <c r="S24" s="413" t="n"/>
+      <c r="Q24" s="411" t="n"/>
+      <c r="R24" s="411" t="n"/>
+      <c r="S24" s="411" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="407" t="n"/>
-      <c r="B25" s="407" t="n"/>
-      <c r="C25" s="407" t="n"/>
-      <c r="D25" s="407" t="n"/>
-      <c r="F25" s="409" t="n"/>
-      <c r="G25" s="409" t="n"/>
-      <c r="H25" s="409" t="n"/>
-      <c r="I25" s="409" t="n"/>
-      <c r="K25" s="411" t="n"/>
-      <c r="L25" s="411" t="n"/>
-      <c r="M25" s="411" t="n"/>
-      <c r="N25" s="411" t="n"/>
-      <c r="P25" s="413" t="n"/>
-      <c r="Q25" s="413" t="n"/>
-      <c r="R25" s="413" t="n"/>
-      <c r="S25" s="413" t="n"/>
+      <c r="A25" s="405" t="n"/>
+      <c r="B25" s="405" t="n"/>
+      <c r="C25" s="405" t="n"/>
+      <c r="D25" s="405" t="n"/>
+      <c r="F25" s="407" t="n"/>
+      <c r="G25" s="407" t="n"/>
+      <c r="H25" s="407" t="n"/>
+      <c r="I25" s="407" t="n"/>
+      <c r="K25" s="409" t="n"/>
+      <c r="L25" s="409" t="n"/>
+      <c r="M25" s="409" t="n"/>
+      <c r="N25" s="409" t="n"/>
+      <c r="P25" s="411" t="n"/>
+      <c r="Q25" s="411" t="n"/>
+      <c r="R25" s="411" t="n"/>
+      <c r="S25" s="411" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -12263,44 +12261,44 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="414" t="inlineStr">
+      <c r="A29" s="412" t="inlineStr">
         <is>
           <t>MH21</t>
         </is>
       </c>
-      <c r="B29" s="415" t="n"/>
-      <c r="C29" s="415" t="n"/>
-      <c r="D29" s="415" t="n"/>
-      <c r="F29" s="416" t="inlineStr">
+      <c r="B29" s="413" t="n"/>
+      <c r="C29" s="413" t="n"/>
+      <c r="D29" s="413" t="n"/>
+      <c r="F29" s="414" t="inlineStr">
         <is>
           <t>MH22</t>
         </is>
       </c>
-      <c r="G29" s="417" t="n"/>
-      <c r="H29" s="417" t="n"/>
-      <c r="I29" s="417" t="n"/>
-      <c r="K29" s="418" t="inlineStr">
+      <c r="G29" s="415" t="n"/>
+      <c r="H29" s="415" t="n"/>
+      <c r="I29" s="415" t="n"/>
+      <c r="K29" s="416" t="inlineStr">
         <is>
           <t>MH23</t>
         </is>
       </c>
-      <c r="L29" s="419" t="n"/>
-      <c r="M29" s="419" t="n"/>
-      <c r="N29" s="419" t="n"/>
+      <c r="L29" s="417" t="n"/>
+      <c r="M29" s="417" t="n"/>
+      <c r="N29" s="417" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="415" t="n"/>
-      <c r="B30" s="415" t="n"/>
-      <c r="C30" s="415" t="n"/>
-      <c r="D30" s="415" t="n"/>
-      <c r="F30" s="417" t="n"/>
-      <c r="G30" s="417" t="n"/>
-      <c r="H30" s="417" t="n"/>
-      <c r="I30" s="417" t="n"/>
-      <c r="K30" s="419" t="n"/>
-      <c r="L30" s="419" t="n"/>
-      <c r="M30" s="419" t="n"/>
-      <c r="N30" s="419" t="n"/>
+      <c r="A30" s="413" t="n"/>
+      <c r="B30" s="413" t="n"/>
+      <c r="C30" s="413" t="n"/>
+      <c r="D30" s="413" t="n"/>
+      <c r="F30" s="415" t="n"/>
+      <c r="G30" s="415" t="n"/>
+      <c r="H30" s="415" t="n"/>
+      <c r="I30" s="415" t="n"/>
+      <c r="K30" s="417" t="n"/>
+      <c r="L30" s="417" t="n"/>
+      <c r="M30" s="417" t="n"/>
+      <c r="N30" s="417" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">

--- a/artkal-m-221-official/colors.xlsx
+++ b/artkal-m-221-official/colors.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_MA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_MB" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_MC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_MD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_ME" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_MF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_MG" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_MH" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_MM" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_MA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_MB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_MC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_ME" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_MH" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_MM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,7 +59,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="222">
+  <fills count="223">
     <fill>
       <patternFill/>
     </fill>
@@ -984,6 +984,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1193,7 +1198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="448">
+  <cellXfs count="449">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1941,12 +1946,9 @@
     <xf numFmtId="0" fontId="5" fillId="185" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="186" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="185" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="186" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="186" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="187" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="187" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="187" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1962,7 +1964,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="190" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="191" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1994,11 +1996,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="198" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="199" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="199" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="199" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="200" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="200" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="200" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2030,7 +2032,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="207" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="208" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="208" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="208" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2038,7 +2040,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="209" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="210" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="210" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="210" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2054,11 +2056,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="213" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="214" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="214" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="214" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="215" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="215" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="215" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2070,22 +2072,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="217" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="218" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="218" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="218" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="219" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="219" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="219" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="220" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="220" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="220" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="221" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="221" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="221" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="222" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="222" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2633,56 +2639,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="418" t="inlineStr">
+      <c r="A4" s="419" t="inlineStr">
         <is>
           <t>MM1</t>
         </is>
       </c>
-      <c r="B4" s="419" t="n"/>
-      <c r="C4" s="419" t="n"/>
-      <c r="D4" s="419" t="n"/>
-      <c r="F4" s="420" t="inlineStr">
+      <c r="B4" s="420" t="n"/>
+      <c r="C4" s="420" t="n"/>
+      <c r="D4" s="420" t="n"/>
+      <c r="F4" s="421" t="inlineStr">
         <is>
           <t>MM2</t>
         </is>
       </c>
-      <c r="G4" s="421" t="n"/>
-      <c r="H4" s="421" t="n"/>
-      <c r="I4" s="421" t="n"/>
-      <c r="K4" s="422" t="inlineStr">
+      <c r="G4" s="422" t="n"/>
+      <c r="H4" s="422" t="n"/>
+      <c r="I4" s="422" t="n"/>
+      <c r="K4" s="423" t="inlineStr">
         <is>
           <t>MM3</t>
         </is>
       </c>
-      <c r="L4" s="423" t="n"/>
-      <c r="M4" s="423" t="n"/>
-      <c r="N4" s="423" t="n"/>
-      <c r="P4" s="424" t="inlineStr">
+      <c r="L4" s="424" t="n"/>
+      <c r="M4" s="424" t="n"/>
+      <c r="N4" s="424" t="n"/>
+      <c r="P4" s="425" t="inlineStr">
         <is>
           <t>MM4</t>
         </is>
       </c>
-      <c r="Q4" s="425" t="n"/>
-      <c r="R4" s="425" t="n"/>
-      <c r="S4" s="425" t="n"/>
+      <c r="Q4" s="426" t="n"/>
+      <c r="R4" s="426" t="n"/>
+      <c r="S4" s="426" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="419" t="n"/>
-      <c r="B5" s="419" t="n"/>
-      <c r="C5" s="419" t="n"/>
-      <c r="D5" s="419" t="n"/>
-      <c r="F5" s="421" t="n"/>
-      <c r="G5" s="421" t="n"/>
-      <c r="H5" s="421" t="n"/>
-      <c r="I5" s="421" t="n"/>
-      <c r="K5" s="423" t="n"/>
-      <c r="L5" s="423" t="n"/>
-      <c r="M5" s="423" t="n"/>
-      <c r="N5" s="423" t="n"/>
-      <c r="P5" s="425" t="n"/>
-      <c r="Q5" s="425" t="n"/>
-      <c r="R5" s="425" t="n"/>
-      <c r="S5" s="425" t="n"/>
+      <c r="A5" s="420" t="n"/>
+      <c r="B5" s="420" t="n"/>
+      <c r="C5" s="420" t="n"/>
+      <c r="D5" s="420" t="n"/>
+      <c r="F5" s="422" t="n"/>
+      <c r="G5" s="422" t="n"/>
+      <c r="H5" s="422" t="n"/>
+      <c r="I5" s="422" t="n"/>
+      <c r="K5" s="424" t="n"/>
+      <c r="L5" s="424" t="n"/>
+      <c r="M5" s="424" t="n"/>
+      <c r="N5" s="424" t="n"/>
+      <c r="P5" s="426" t="n"/>
+      <c r="Q5" s="426" t="n"/>
+      <c r="R5" s="426" t="n"/>
+      <c r="S5" s="426" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -2787,56 +2793,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="426" t="inlineStr">
+      <c r="A9" s="427" t="inlineStr">
         <is>
           <t>MM5</t>
         </is>
       </c>
-      <c r="B9" s="427" t="n"/>
-      <c r="C9" s="427" t="n"/>
-      <c r="D9" s="427" t="n"/>
-      <c r="F9" s="428" t="inlineStr">
+      <c r="B9" s="428" t="n"/>
+      <c r="C9" s="428" t="n"/>
+      <c r="D9" s="428" t="n"/>
+      <c r="F9" s="429" t="inlineStr">
         <is>
           <t>MM6</t>
         </is>
       </c>
-      <c r="G9" s="429" t="n"/>
-      <c r="H9" s="429" t="n"/>
-      <c r="I9" s="429" t="n"/>
-      <c r="K9" s="430" t="inlineStr">
+      <c r="G9" s="430" t="n"/>
+      <c r="H9" s="430" t="n"/>
+      <c r="I9" s="430" t="n"/>
+      <c r="K9" s="431" t="inlineStr">
         <is>
           <t>MM7</t>
         </is>
       </c>
-      <c r="L9" s="431" t="n"/>
-      <c r="M9" s="431" t="n"/>
-      <c r="N9" s="431" t="n"/>
-      <c r="P9" s="432" t="inlineStr">
+      <c r="L9" s="432" t="n"/>
+      <c r="M9" s="432" t="n"/>
+      <c r="N9" s="432" t="n"/>
+      <c r="P9" s="433" t="inlineStr">
         <is>
           <t>MM8</t>
         </is>
       </c>
-      <c r="Q9" s="433" t="n"/>
-      <c r="R9" s="433" t="n"/>
-      <c r="S9" s="433" t="n"/>
+      <c r="Q9" s="434" t="n"/>
+      <c r="R9" s="434" t="n"/>
+      <c r="S9" s="434" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="427" t="n"/>
-      <c r="B10" s="427" t="n"/>
-      <c r="C10" s="427" t="n"/>
-      <c r="D10" s="427" t="n"/>
-      <c r="F10" s="429" t="n"/>
-      <c r="G10" s="429" t="n"/>
-      <c r="H10" s="429" t="n"/>
-      <c r="I10" s="429" t="n"/>
-      <c r="K10" s="431" t="n"/>
-      <c r="L10" s="431" t="n"/>
-      <c r="M10" s="431" t="n"/>
-      <c r="N10" s="431" t="n"/>
-      <c r="P10" s="433" t="n"/>
-      <c r="Q10" s="433" t="n"/>
-      <c r="R10" s="433" t="n"/>
-      <c r="S10" s="433" t="n"/>
+      <c r="A10" s="428" t="n"/>
+      <c r="B10" s="428" t="n"/>
+      <c r="C10" s="428" t="n"/>
+      <c r="D10" s="428" t="n"/>
+      <c r="F10" s="430" t="n"/>
+      <c r="G10" s="430" t="n"/>
+      <c r="H10" s="430" t="n"/>
+      <c r="I10" s="430" t="n"/>
+      <c r="K10" s="432" t="n"/>
+      <c r="L10" s="432" t="n"/>
+      <c r="M10" s="432" t="n"/>
+      <c r="N10" s="432" t="n"/>
+      <c r="P10" s="434" t="n"/>
+      <c r="Q10" s="434" t="n"/>
+      <c r="R10" s="434" t="n"/>
+      <c r="S10" s="434" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -2941,56 +2947,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="434" t="inlineStr">
+      <c r="A14" s="435" t="inlineStr">
         <is>
           <t>MM9</t>
         </is>
       </c>
-      <c r="B14" s="435" t="n"/>
-      <c r="C14" s="435" t="n"/>
-      <c r="D14" s="435" t="n"/>
-      <c r="F14" s="436" t="inlineStr">
+      <c r="B14" s="436" t="n"/>
+      <c r="C14" s="436" t="n"/>
+      <c r="D14" s="436" t="n"/>
+      <c r="F14" s="437" t="inlineStr">
         <is>
           <t>MM10</t>
         </is>
       </c>
-      <c r="G14" s="437" t="n"/>
-      <c r="H14" s="437" t="n"/>
-      <c r="I14" s="437" t="n"/>
-      <c r="K14" s="438" t="inlineStr">
+      <c r="G14" s="438" t="n"/>
+      <c r="H14" s="438" t="n"/>
+      <c r="I14" s="438" t="n"/>
+      <c r="K14" s="439" t="inlineStr">
         <is>
           <t>MM11</t>
         </is>
       </c>
-      <c r="L14" s="439" t="n"/>
-      <c r="M14" s="439" t="n"/>
-      <c r="N14" s="439" t="n"/>
-      <c r="P14" s="440" t="inlineStr">
+      <c r="L14" s="440" t="n"/>
+      <c r="M14" s="440" t="n"/>
+      <c r="N14" s="440" t="n"/>
+      <c r="P14" s="441" t="inlineStr">
         <is>
           <t>MM12</t>
         </is>
       </c>
-      <c r="Q14" s="441" t="n"/>
-      <c r="R14" s="441" t="n"/>
-      <c r="S14" s="441" t="n"/>
+      <c r="Q14" s="442" t="n"/>
+      <c r="R14" s="442" t="n"/>
+      <c r="S14" s="442" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="435" t="n"/>
-      <c r="B15" s="435" t="n"/>
-      <c r="C15" s="435" t="n"/>
-      <c r="D15" s="435" t="n"/>
-      <c r="F15" s="437" t="n"/>
-      <c r="G15" s="437" t="n"/>
-      <c r="H15" s="437" t="n"/>
-      <c r="I15" s="437" t="n"/>
-      <c r="K15" s="439" t="n"/>
-      <c r="L15" s="439" t="n"/>
-      <c r="M15" s="439" t="n"/>
-      <c r="N15" s="439" t="n"/>
-      <c r="P15" s="441" t="n"/>
-      <c r="Q15" s="441" t="n"/>
-      <c r="R15" s="441" t="n"/>
-      <c r="S15" s="441" t="n"/>
+      <c r="A15" s="436" t="n"/>
+      <c r="B15" s="436" t="n"/>
+      <c r="C15" s="436" t="n"/>
+      <c r="D15" s="436" t="n"/>
+      <c r="F15" s="438" t="n"/>
+      <c r="G15" s="438" t="n"/>
+      <c r="H15" s="438" t="n"/>
+      <c r="I15" s="438" t="n"/>
+      <c r="K15" s="440" t="n"/>
+      <c r="L15" s="440" t="n"/>
+      <c r="M15" s="440" t="n"/>
+      <c r="N15" s="440" t="n"/>
+      <c r="P15" s="442" t="n"/>
+      <c r="Q15" s="442" t="n"/>
+      <c r="R15" s="442" t="n"/>
+      <c r="S15" s="442" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3095,44 +3101,44 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="442" t="inlineStr">
+      <c r="A19" s="443" t="inlineStr">
         <is>
           <t>MM13</t>
         </is>
       </c>
-      <c r="B19" s="443" t="n"/>
-      <c r="C19" s="443" t="n"/>
-      <c r="D19" s="443" t="n"/>
-      <c r="F19" s="444" t="inlineStr">
+      <c r="B19" s="444" t="n"/>
+      <c r="C19" s="444" t="n"/>
+      <c r="D19" s="444" t="n"/>
+      <c r="F19" s="445" t="inlineStr">
         <is>
           <t>MM14</t>
         </is>
       </c>
-      <c r="G19" s="445" t="n"/>
-      <c r="H19" s="445" t="n"/>
-      <c r="I19" s="445" t="n"/>
-      <c r="K19" s="446" t="inlineStr">
+      <c r="G19" s="446" t="n"/>
+      <c r="H19" s="446" t="n"/>
+      <c r="I19" s="446" t="n"/>
+      <c r="K19" s="447" t="inlineStr">
         <is>
           <t>MM15</t>
         </is>
       </c>
-      <c r="L19" s="447" t="n"/>
-      <c r="M19" s="447" t="n"/>
-      <c r="N19" s="447" t="n"/>
+      <c r="L19" s="448" t="n"/>
+      <c r="M19" s="448" t="n"/>
+      <c r="N19" s="448" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="443" t="n"/>
-      <c r="B20" s="443" t="n"/>
-      <c r="C20" s="443" t="n"/>
-      <c r="D20" s="443" t="n"/>
-      <c r="F20" s="445" t="n"/>
-      <c r="G20" s="445" t="n"/>
-      <c r="H20" s="445" t="n"/>
-      <c r="I20" s="445" t="n"/>
-      <c r="K20" s="447" t="n"/>
-      <c r="L20" s="447" t="n"/>
-      <c r="M20" s="447" t="n"/>
-      <c r="N20" s="447" t="n"/>
+      <c r="A20" s="444" t="n"/>
+      <c r="B20" s="444" t="n"/>
+      <c r="C20" s="444" t="n"/>
+      <c r="D20" s="444" t="n"/>
+      <c r="F20" s="446" t="n"/>
+      <c r="G20" s="446" t="n"/>
+      <c r="H20" s="446" t="n"/>
+      <c r="I20" s="446" t="n"/>
+      <c r="K20" s="448" t="n"/>
+      <c r="L20" s="448" t="n"/>
+      <c r="M20" s="448" t="n"/>
+      <c r="N20" s="448" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -11497,55 +11503,55 @@
         </is>
       </c>
       <c r="B4" s="375" t="n"/>
-      <c r="C4" s="375" t="n"/>
+      <c r="C4" s="376" t="n"/>
       <c r="D4" s="375" t="n"/>
       <c r="F4" s="374" t="inlineStr">
         <is>
           <t>MH2</t>
         </is>
       </c>
-      <c r="G4" s="375" t="n"/>
-      <c r="H4" s="375" t="n"/>
-      <c r="I4" s="375" t="n"/>
-      <c r="K4" s="376" t="inlineStr">
+      <c r="G4" s="376" t="n"/>
+      <c r="H4" s="376" t="n"/>
+      <c r="I4" s="376" t="n"/>
+      <c r="K4" s="377" t="inlineStr">
         <is>
           <t>MH3</t>
         </is>
       </c>
-      <c r="L4" s="377" t="n"/>
-      <c r="M4" s="377" t="n"/>
-      <c r="N4" s="377" t="n"/>
-      <c r="P4" s="378" t="inlineStr">
+      <c r="L4" s="378" t="n"/>
+      <c r="M4" s="378" t="n"/>
+      <c r="N4" s="378" t="n"/>
+      <c r="P4" s="379" t="inlineStr">
         <is>
           <t>MH4</t>
         </is>
       </c>
-      <c r="Q4" s="379" t="n"/>
-      <c r="R4" s="379" t="n"/>
-      <c r="S4" s="379" t="n"/>
+      <c r="Q4" s="380" t="n"/>
+      <c r="R4" s="380" t="n"/>
+      <c r="S4" s="380" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="375" t="n"/>
-      <c r="B5" s="375" t="n"/>
+      <c r="B5" s="376" t="n"/>
       <c r="C5" s="375" t="n"/>
-      <c r="D5" s="375" t="n"/>
-      <c r="F5" s="375" t="n"/>
-      <c r="G5" s="375" t="n"/>
-      <c r="H5" s="375" t="n"/>
-      <c r="I5" s="375" t="n"/>
-      <c r="K5" s="377" t="n"/>
-      <c r="L5" s="377" t="n"/>
-      <c r="M5" s="377" t="n"/>
-      <c r="N5" s="377" t="n"/>
-      <c r="P5" s="379" t="n"/>
-      <c r="Q5" s="379" t="n"/>
-      <c r="R5" s="379" t="n"/>
-      <c r="S5" s="379" t="n"/>
+      <c r="D5" s="376" t="n"/>
+      <c r="F5" s="376" t="n"/>
+      <c r="G5" s="376" t="n"/>
+      <c r="H5" s="376" t="n"/>
+      <c r="I5" s="376" t="n"/>
+      <c r="K5" s="378" t="n"/>
+      <c r="L5" s="378" t="n"/>
+      <c r="M5" s="378" t="n"/>
+      <c r="N5" s="378" t="n"/>
+      <c r="P5" s="380" t="n"/>
+      <c r="Q5" s="380" t="n"/>
+      <c r="R5" s="380" t="n"/>
+      <c r="S5" s="380" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: #FFFFFF</t>
+          <t>HEX: #FFFFFF00</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -11579,7 +11585,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: 255, 255, 255</t>
+          <t>RGB: 255, 255, 255, 0</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -11645,56 +11651,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="380" t="inlineStr">
+      <c r="A9" s="381" t="inlineStr">
         <is>
           <t>MH5</t>
         </is>
       </c>
-      <c r="B9" s="381" t="n"/>
-      <c r="C9" s="381" t="n"/>
-      <c r="D9" s="381" t="n"/>
-      <c r="F9" s="382" t="inlineStr">
+      <c r="B9" s="382" t="n"/>
+      <c r="C9" s="382" t="n"/>
+      <c r="D9" s="382" t="n"/>
+      <c r="F9" s="383" t="inlineStr">
         <is>
           <t>MH6</t>
         </is>
       </c>
-      <c r="G9" s="383" t="n"/>
-      <c r="H9" s="383" t="n"/>
-      <c r="I9" s="383" t="n"/>
-      <c r="K9" s="384" t="inlineStr">
+      <c r="G9" s="384" t="n"/>
+      <c r="H9" s="384" t="n"/>
+      <c r="I9" s="384" t="n"/>
+      <c r="K9" s="385" t="inlineStr">
         <is>
           <t>MH7</t>
         </is>
       </c>
-      <c r="L9" s="385" t="n"/>
-      <c r="M9" s="385" t="n"/>
-      <c r="N9" s="385" t="n"/>
-      <c r="P9" s="386" t="inlineStr">
+      <c r="L9" s="386" t="n"/>
+      <c r="M9" s="386" t="n"/>
+      <c r="N9" s="386" t="n"/>
+      <c r="P9" s="387" t="inlineStr">
         <is>
           <t>MH8</t>
         </is>
       </c>
-      <c r="Q9" s="387" t="n"/>
-      <c r="R9" s="387" t="n"/>
-      <c r="S9" s="387" t="n"/>
+      <c r="Q9" s="388" t="n"/>
+      <c r="R9" s="388" t="n"/>
+      <c r="S9" s="388" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="381" t="n"/>
-      <c r="B10" s="381" t="n"/>
-      <c r="C10" s="381" t="n"/>
-      <c r="D10" s="381" t="n"/>
-      <c r="F10" s="383" t="n"/>
-      <c r="G10" s="383" t="n"/>
-      <c r="H10" s="383" t="n"/>
-      <c r="I10" s="383" t="n"/>
-      <c r="K10" s="385" t="n"/>
-      <c r="L10" s="385" t="n"/>
-      <c r="M10" s="385" t="n"/>
-      <c r="N10" s="385" t="n"/>
-      <c r="P10" s="387" t="n"/>
-      <c r="Q10" s="387" t="n"/>
-      <c r="R10" s="387" t="n"/>
-      <c r="S10" s="387" t="n"/>
+      <c r="A10" s="382" t="n"/>
+      <c r="B10" s="382" t="n"/>
+      <c r="C10" s="382" t="n"/>
+      <c r="D10" s="382" t="n"/>
+      <c r="F10" s="384" t="n"/>
+      <c r="G10" s="384" t="n"/>
+      <c r="H10" s="384" t="n"/>
+      <c r="I10" s="384" t="n"/>
+      <c r="K10" s="386" t="n"/>
+      <c r="L10" s="386" t="n"/>
+      <c r="M10" s="386" t="n"/>
+      <c r="N10" s="386" t="n"/>
+      <c r="P10" s="388" t="n"/>
+      <c r="Q10" s="388" t="n"/>
+      <c r="R10" s="388" t="n"/>
+      <c r="S10" s="388" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -11799,56 +11805,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="388" t="inlineStr">
+      <c r="A14" s="389" t="inlineStr">
         <is>
           <t>MH9</t>
         </is>
       </c>
-      <c r="B14" s="389" t="n"/>
-      <c r="C14" s="389" t="n"/>
-      <c r="D14" s="389" t="n"/>
-      <c r="F14" s="390" t="inlineStr">
+      <c r="B14" s="390" t="n"/>
+      <c r="C14" s="390" t="n"/>
+      <c r="D14" s="390" t="n"/>
+      <c r="F14" s="391" t="inlineStr">
         <is>
           <t>MH10</t>
         </is>
       </c>
-      <c r="G14" s="391" t="n"/>
-      <c r="H14" s="391" t="n"/>
-      <c r="I14" s="391" t="n"/>
-      <c r="K14" s="392" t="inlineStr">
+      <c r="G14" s="392" t="n"/>
+      <c r="H14" s="392" t="n"/>
+      <c r="I14" s="392" t="n"/>
+      <c r="K14" s="393" t="inlineStr">
         <is>
           <t>MH11</t>
         </is>
       </c>
-      <c r="L14" s="393" t="n"/>
-      <c r="M14" s="393" t="n"/>
-      <c r="N14" s="393" t="n"/>
-      <c r="P14" s="394" t="inlineStr">
+      <c r="L14" s="394" t="n"/>
+      <c r="M14" s="394" t="n"/>
+      <c r="N14" s="394" t="n"/>
+      <c r="P14" s="395" t="inlineStr">
         <is>
           <t>MH12</t>
         </is>
       </c>
-      <c r="Q14" s="395" t="n"/>
-      <c r="R14" s="395" t="n"/>
-      <c r="S14" s="395" t="n"/>
+      <c r="Q14" s="396" t="n"/>
+      <c r="R14" s="396" t="n"/>
+      <c r="S14" s="396" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="389" t="n"/>
-      <c r="B15" s="389" t="n"/>
-      <c r="C15" s="389" t="n"/>
-      <c r="D15" s="389" t="n"/>
-      <c r="F15" s="391" t="n"/>
-      <c r="G15" s="391" t="n"/>
-      <c r="H15" s="391" t="n"/>
-      <c r="I15" s="391" t="n"/>
-      <c r="K15" s="393" t="n"/>
-      <c r="L15" s="393" t="n"/>
-      <c r="M15" s="393" t="n"/>
-      <c r="N15" s="393" t="n"/>
-      <c r="P15" s="395" t="n"/>
-      <c r="Q15" s="395" t="n"/>
-      <c r="R15" s="395" t="n"/>
-      <c r="S15" s="395" t="n"/>
+      <c r="A15" s="390" t="n"/>
+      <c r="B15" s="390" t="n"/>
+      <c r="C15" s="390" t="n"/>
+      <c r="D15" s="390" t="n"/>
+      <c r="F15" s="392" t="n"/>
+      <c r="G15" s="392" t="n"/>
+      <c r="H15" s="392" t="n"/>
+      <c r="I15" s="392" t="n"/>
+      <c r="K15" s="394" t="n"/>
+      <c r="L15" s="394" t="n"/>
+      <c r="M15" s="394" t="n"/>
+      <c r="N15" s="394" t="n"/>
+      <c r="P15" s="396" t="n"/>
+      <c r="Q15" s="396" t="n"/>
+      <c r="R15" s="396" t="n"/>
+      <c r="S15" s="396" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -11953,56 +11959,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="396" t="inlineStr">
+      <c r="A19" s="397" t="inlineStr">
         <is>
           <t>MH13</t>
         </is>
       </c>
-      <c r="B19" s="397" t="n"/>
-      <c r="C19" s="397" t="n"/>
-      <c r="D19" s="397" t="n"/>
-      <c r="F19" s="398" t="inlineStr">
+      <c r="B19" s="398" t="n"/>
+      <c r="C19" s="398" t="n"/>
+      <c r="D19" s="398" t="n"/>
+      <c r="F19" s="399" t="inlineStr">
         <is>
           <t>MH14</t>
         </is>
       </c>
-      <c r="G19" s="399" t="n"/>
-      <c r="H19" s="399" t="n"/>
-      <c r="I19" s="399" t="n"/>
-      <c r="K19" s="400" t="inlineStr">
+      <c r="G19" s="400" t="n"/>
+      <c r="H19" s="400" t="n"/>
+      <c r="I19" s="400" t="n"/>
+      <c r="K19" s="401" t="inlineStr">
         <is>
           <t>MH15</t>
         </is>
       </c>
-      <c r="L19" s="401" t="n"/>
-      <c r="M19" s="401" t="n"/>
-      <c r="N19" s="401" t="n"/>
-      <c r="P19" s="402" t="inlineStr">
+      <c r="L19" s="402" t="n"/>
+      <c r="M19" s="402" t="n"/>
+      <c r="N19" s="402" t="n"/>
+      <c r="P19" s="403" t="inlineStr">
         <is>
           <t>MH16</t>
         </is>
       </c>
-      <c r="Q19" s="403" t="n"/>
-      <c r="R19" s="403" t="n"/>
-      <c r="S19" s="403" t="n"/>
+      <c r="Q19" s="404" t="n"/>
+      <c r="R19" s="404" t="n"/>
+      <c r="S19" s="404" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="397" t="n"/>
-      <c r="B20" s="397" t="n"/>
-      <c r="C20" s="397" t="n"/>
-      <c r="D20" s="397" t="n"/>
-      <c r="F20" s="399" t="n"/>
-      <c r="G20" s="399" t="n"/>
-      <c r="H20" s="399" t="n"/>
-      <c r="I20" s="399" t="n"/>
-      <c r="K20" s="401" t="n"/>
-      <c r="L20" s="401" t="n"/>
-      <c r="M20" s="401" t="n"/>
-      <c r="N20" s="401" t="n"/>
-      <c r="P20" s="403" t="n"/>
-      <c r="Q20" s="403" t="n"/>
-      <c r="R20" s="403" t="n"/>
-      <c r="S20" s="403" t="n"/>
+      <c r="A20" s="398" t="n"/>
+      <c r="B20" s="398" t="n"/>
+      <c r="C20" s="398" t="n"/>
+      <c r="D20" s="398" t="n"/>
+      <c r="F20" s="400" t="n"/>
+      <c r="G20" s="400" t="n"/>
+      <c r="H20" s="400" t="n"/>
+      <c r="I20" s="400" t="n"/>
+      <c r="K20" s="402" t="n"/>
+      <c r="L20" s="402" t="n"/>
+      <c r="M20" s="402" t="n"/>
+      <c r="N20" s="402" t="n"/>
+      <c r="P20" s="404" t="n"/>
+      <c r="Q20" s="404" t="n"/>
+      <c r="R20" s="404" t="n"/>
+      <c r="S20" s="404" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -12107,56 +12113,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="404" t="inlineStr">
+      <c r="A24" s="405" t="inlineStr">
         <is>
           <t>MH17</t>
         </is>
       </c>
-      <c r="B24" s="405" t="n"/>
-      <c r="C24" s="405" t="n"/>
-      <c r="D24" s="405" t="n"/>
-      <c r="F24" s="406" t="inlineStr">
+      <c r="B24" s="406" t="n"/>
+      <c r="C24" s="406" t="n"/>
+      <c r="D24" s="406" t="n"/>
+      <c r="F24" s="407" t="inlineStr">
         <is>
           <t>MH18</t>
         </is>
       </c>
-      <c r="G24" s="407" t="n"/>
-      <c r="H24" s="407" t="n"/>
-      <c r="I24" s="407" t="n"/>
-      <c r="K24" s="408" t="inlineStr">
+      <c r="G24" s="408" t="n"/>
+      <c r="H24" s="408" t="n"/>
+      <c r="I24" s="408" t="n"/>
+      <c r="K24" s="409" t="inlineStr">
         <is>
           <t>MH19</t>
         </is>
       </c>
-      <c r="L24" s="409" t="n"/>
-      <c r="M24" s="409" t="n"/>
-      <c r="N24" s="409" t="n"/>
-      <c r="P24" s="410" t="inlineStr">
+      <c r="L24" s="410" t="n"/>
+      <c r="M24" s="410" t="n"/>
+      <c r="N24" s="410" t="n"/>
+      <c r="P24" s="411" t="inlineStr">
         <is>
           <t>MH20</t>
         </is>
       </c>
-      <c r="Q24" s="411" t="n"/>
-      <c r="R24" s="411" t="n"/>
-      <c r="S24" s="411" t="n"/>
+      <c r="Q24" s="412" t="n"/>
+      <c r="R24" s="412" t="n"/>
+      <c r="S24" s="412" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="405" t="n"/>
-      <c r="B25" s="405" t="n"/>
-      <c r="C25" s="405" t="n"/>
-      <c r="D25" s="405" t="n"/>
-      <c r="F25" s="407" t="n"/>
-      <c r="G25" s="407" t="n"/>
-      <c r="H25" s="407" t="n"/>
-      <c r="I25" s="407" t="n"/>
-      <c r="K25" s="409" t="n"/>
-      <c r="L25" s="409" t="n"/>
-      <c r="M25" s="409" t="n"/>
-      <c r="N25" s="409" t="n"/>
-      <c r="P25" s="411" t="n"/>
-      <c r="Q25" s="411" t="n"/>
-      <c r="R25" s="411" t="n"/>
-      <c r="S25" s="411" t="n"/>
+      <c r="A25" s="406" t="n"/>
+      <c r="B25" s="406" t="n"/>
+      <c r="C25" s="406" t="n"/>
+      <c r="D25" s="406" t="n"/>
+      <c r="F25" s="408" t="n"/>
+      <c r="G25" s="408" t="n"/>
+      <c r="H25" s="408" t="n"/>
+      <c r="I25" s="408" t="n"/>
+      <c r="K25" s="410" t="n"/>
+      <c r="L25" s="410" t="n"/>
+      <c r="M25" s="410" t="n"/>
+      <c r="N25" s="410" t="n"/>
+      <c r="P25" s="412" t="n"/>
+      <c r="Q25" s="412" t="n"/>
+      <c r="R25" s="412" t="n"/>
+      <c r="S25" s="412" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -12261,44 +12267,44 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="412" t="inlineStr">
+      <c r="A29" s="413" t="inlineStr">
         <is>
           <t>MH21</t>
         </is>
       </c>
-      <c r="B29" s="413" t="n"/>
-      <c r="C29" s="413" t="n"/>
-      <c r="D29" s="413" t="n"/>
-      <c r="F29" s="414" t="inlineStr">
+      <c r="B29" s="414" t="n"/>
+      <c r="C29" s="414" t="n"/>
+      <c r="D29" s="414" t="n"/>
+      <c r="F29" s="415" t="inlineStr">
         <is>
           <t>MH22</t>
         </is>
       </c>
-      <c r="G29" s="415" t="n"/>
-      <c r="H29" s="415" t="n"/>
-      <c r="I29" s="415" t="n"/>
-      <c r="K29" s="416" t="inlineStr">
+      <c r="G29" s="416" t="n"/>
+      <c r="H29" s="416" t="n"/>
+      <c r="I29" s="416" t="n"/>
+      <c r="K29" s="417" t="inlineStr">
         <is>
           <t>MH23</t>
         </is>
       </c>
-      <c r="L29" s="417" t="n"/>
-      <c r="M29" s="417" t="n"/>
-      <c r="N29" s="417" t="n"/>
+      <c r="L29" s="418" t="n"/>
+      <c r="M29" s="418" t="n"/>
+      <c r="N29" s="418" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="413" t="n"/>
-      <c r="B30" s="413" t="n"/>
-      <c r="C30" s="413" t="n"/>
-      <c r="D30" s="413" t="n"/>
-      <c r="F30" s="415" t="n"/>
-      <c r="G30" s="415" t="n"/>
-      <c r="H30" s="415" t="n"/>
-      <c r="I30" s="415" t="n"/>
-      <c r="K30" s="417" t="n"/>
-      <c r="L30" s="417" t="n"/>
-      <c r="M30" s="417" t="n"/>
-      <c r="N30" s="417" t="n"/>
+      <c r="A30" s="414" t="n"/>
+      <c r="B30" s="414" t="n"/>
+      <c r="C30" s="414" t="n"/>
+      <c r="D30" s="414" t="n"/>
+      <c r="F30" s="416" t="n"/>
+      <c r="G30" s="416" t="n"/>
+      <c r="H30" s="416" t="n"/>
+      <c r="I30" s="416" t="n"/>
+      <c r="K30" s="418" t="n"/>
+      <c r="L30" s="418" t="n"/>
+      <c r="M30" s="418" t="n"/>
+      <c r="N30" s="418" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -12379,7 +12385,7 @@
       <c r="N33" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="91">
     <mergeCell ref="F27:I27"/>
     <mergeCell ref="P18:S18"/>
     <mergeCell ref="P9:S10"/>
@@ -12412,7 +12418,6 @@
     <mergeCell ref="A14:D15"/>
     <mergeCell ref="P19:S20"/>
     <mergeCell ref="K21:N21"/>
-    <mergeCell ref="A4:D5"/>
     <mergeCell ref="K4:N5"/>
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="F33:I33"/>
